--- a/data/trans_bre/P8_1_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P8_1_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,22; 21,48</t>
+          <t>14,44; 21,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,52; 21,07</t>
+          <t>12,42; 20,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,03; 19,32</t>
+          <t>10,11; 19,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,06; 24,88</t>
+          <t>14,97; 24,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>55,06; 98,77</t>
+          <t>57,56; 102,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,79; 72,48</t>
+          <t>35,94; 71,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,27; 63,84</t>
+          <t>28,77; 64,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>41,56; 82,21</t>
+          <t>41,79; 81,33</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,49</t>
+          <t>1,04; 4,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 6,05</t>
+          <t>1,91; 6,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 7,31</t>
+          <t>3,04; 7,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,61; 1,31</t>
+          <t>-29,98; 1,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,5; 91,49</t>
+          <t>16,88; 94,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,26; 85,83</t>
+          <t>22,29; 86,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,53; 89,56</t>
+          <t>31,28; 93,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-74,0; 11,09</t>
+          <t>-72,65; 10,7</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,68</t>
+          <t>0,82; 7,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 5,54</t>
+          <t>-2,43; 5,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 4,72</t>
+          <t>-2,07; 4,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 4,43</t>
+          <t>-0,44; 4,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,93; 209,57</t>
+          <t>7,15; 193,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-28,83; 104,38</t>
+          <t>-29,26; 94,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-25,41; 85,6</t>
+          <t>-25,0; 90,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 89,83</t>
+          <t>-5,67; 85,83</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,48; 12,04</t>
+          <t>8,41; 12,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,7; 12,51</t>
+          <t>8,64; 12,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,92; 10,57</t>
+          <t>6,87; 10,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,89; 6,81</t>
+          <t>-19,26; 7,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>71,36; 115,43</t>
+          <t>70,26; 115,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,54; 91,01</t>
+          <t>55,19; 92,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,61; 80,01</t>
+          <t>46,59; 82,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,81; 46,32</t>
+          <t>-49,74; 48,97</t>
         </is>
       </c>
     </row>
